--- a/自考本科/个人学习笔记/Byvm815/考试时间安排表.xlsx
+++ b/自考本科/个人学习笔记/Byvm815/考试时间安排表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8310"/>
+    <workbookView windowWidth="23040" windowHeight="10710"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -113,7 +113,8 @@
 免考13013-高级语言程序设计</t>
   </si>
   <si>
-    <t>实践科目</t>
+    <t>(深圳大学)
+实践科目</t>
   </si>
   <si>
     <t>03345-信息与网络安全管理</t>
@@ -137,10 +138,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -172,16 +173,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color indexed="4"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -195,55 +189,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color indexed="65"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color indexed="20"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -258,8 +204,8 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -267,28 +213,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="2"/>
+      <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -308,6 +233,82 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color indexed="20"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="65"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="2"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color indexed="4"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="37">
     <fill>
@@ -342,37 +343,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="26"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="47"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -384,145 +523,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="26"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="47"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -608,35 +609,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -652,6 +629,30 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -673,6 +674,30 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -681,179 +706,155 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="11" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" applyNumberFormat="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="10" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="10" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="13" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="11" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="10" applyNumberFormat="0" applyFont="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="14" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="14" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="7" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -917,6 +918,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1253,18 +1257,18 @@
       <c r="C2" s="10"/>
       <c r="D2" s="10"/>
       <c r="E2" s="10"/>
-      <c r="G2" s="26" t="s">
+      <c r="G2" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="L2" s="26" t="s">
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="L2" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:15">
       <c r="A3" s="8"/>
@@ -1319,16 +1323,16 @@
       <c r="E4" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="27" t="s">
+      <c r="G4" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="27" t="s">
+      <c r="H4" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="27" t="s">
+      <c r="I4" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J4" s="27" t="s">
+      <c r="J4" s="28" t="s">
         <v>12</v>
       </c>
       <c r="L4" s="12" t="s">
@@ -1352,18 +1356,18 @@
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
       <c r="E5" s="10"/>
-      <c r="G5" s="28" t="s">
+      <c r="G5" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="28"/>
-      <c r="L5" s="28" t="s">
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
+      <c r="L5" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="M5" s="28"/>
-      <c r="N5" s="28"/>
-      <c r="O5" s="28"/>
+      <c r="M5" s="29"/>
+      <c r="N5" s="29"/>
+      <c r="O5" s="29"/>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:15">
       <c r="A6" s="8"/>
@@ -1550,18 +1554,18 @@
       <c r="C11" s="10"/>
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
-      <c r="G11" s="28" t="s">
+      <c r="G11" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="H11" s="28"/>
-      <c r="I11" s="28"/>
-      <c r="J11" s="28"/>
-      <c r="L11" s="28" t="s">
+      <c r="H11" s="29"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="29"/>
+      <c r="L11" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="M11" s="28"/>
-      <c r="N11" s="28"/>
-      <c r="O11" s="28"/>
+      <c r="M11" s="29"/>
+      <c r="N11" s="29"/>
+      <c r="O11" s="29"/>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:15">
       <c r="A12" s="8"/>
@@ -1813,10 +1817,10 @@
       <c r="D20" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="E20" s="29" t="s">
+      <c r="E20" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="G20" s="29" t="s">
+      <c r="G20" s="30" t="s">
         <v>29</v>
       </c>
       <c r="H20" s="21" t="s">
@@ -1849,7 +1853,7 @@
       <c r="E21" s="23"/>
     </row>
     <row r="22" s="5" customFormat="1" spans="1:15">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="24" t="s">
         <v>31</v>
       </c>
       <c r="B22" s="20" t="s">
@@ -1879,18 +1883,18 @@
       <c r="C23" s="10"/>
       <c r="D23" s="10"/>
       <c r="E23" s="10"/>
-      <c r="G23" s="26" t="s">
+      <c r="G23" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
-      <c r="J23" s="26"/>
-      <c r="L23" s="26" t="s">
+      <c r="H23" s="27"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="27"/>
+      <c r="L23" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="M23" s="26"/>
-      <c r="N23" s="26"/>
-      <c r="O23" s="26"/>
+      <c r="M23" s="27"/>
+      <c r="N23" s="27"/>
+      <c r="O23" s="27"/>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="8"/>
@@ -1933,40 +1937,40 @@
     </row>
     <row r="25" ht="29.25" spans="1:15">
       <c r="A25" s="8"/>
-      <c r="B25" s="24" t="s">
+      <c r="B25" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="25" t="s">
+      <c r="C25" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="D25" s="25" t="s">
+      <c r="D25" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="E25" s="25" t="s">
+      <c r="E25" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="G25" s="24" t="s">
+      <c r="G25" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="H25" s="30" t="s">
+      <c r="H25" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="I25" s="25" t="s">
+      <c r="I25" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="J25" s="30" t="s">
+      <c r="J25" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="L25" s="24" t="s">
+      <c r="L25" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="M25" s="25" t="s">
+      <c r="M25" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="N25" s="25" t="s">
+      <c r="N25" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="O25" s="25" t="s">
+      <c r="O25" s="26" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1978,18 +1982,18 @@
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
-      <c r="G26" s="28" t="s">
+      <c r="G26" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="H26" s="28"/>
-      <c r="I26" s="28"/>
-      <c r="J26" s="28"/>
-      <c r="L26" s="28" t="s">
+      <c r="H26" s="29"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="29"/>
+      <c r="L26" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="M26" s="28"/>
-      <c r="N26" s="28"/>
-      <c r="O26" s="28"/>
+      <c r="M26" s="29"/>
+      <c r="N26" s="29"/>
+      <c r="O26" s="29"/>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="8"/>
@@ -2032,66 +2036,66 @@
     </row>
     <row r="28" ht="29.25" spans="1:15">
       <c r="A28" s="8"/>
-      <c r="B28" s="24" t="s">
+      <c r="B28" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="25" t="s">
+      <c r="C28" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="D28" s="25" t="s">
+      <c r="D28" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="E28" s="25" t="s">
+      <c r="E28" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="G28" s="31" t="s">
+      <c r="G28" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="H28" s="25" t="s">
+      <c r="H28" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="I28" s="30" t="s">
+      <c r="I28" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="J28" s="25" t="s">
+      <c r="J28" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="L28" s="24" t="s">
+      <c r="L28" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="M28" s="25" t="s">
+      <c r="M28" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="N28" s="25" t="s">
+      <c r="N28" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="O28" s="25" t="s">
+      <c r="O28" s="26" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="32" spans="7:8">
-      <c r="G32" s="32"/>
-      <c r="H32" s="32"/>
+      <c r="G32" s="33"/>
+      <c r="H32" s="33"/>
     </row>
     <row r="33" spans="7:8">
       <c r="G33" s="10"/>
       <c r="H33" s="10"/>
     </row>
     <row r="34" spans="7:8">
-      <c r="G34" s="33"/>
-      <c r="H34" s="33"/>
+      <c r="G34" s="34"/>
+      <c r="H34" s="34"/>
     </row>
     <row r="35" spans="7:8">
-      <c r="G35" s="34"/>
-      <c r="H35" s="34"/>
+      <c r="G35" s="35"/>
+      <c r="H35" s="35"/>
     </row>
     <row r="36" spans="7:8">
-      <c r="G36" s="33"/>
-      <c r="H36" s="33"/>
+      <c r="G36" s="34"/>
+      <c r="H36" s="34"/>
     </row>
     <row r="37" spans="7:8">
-      <c r="G37" s="33"/>
-      <c r="H37" s="33"/>
+      <c r="G37" s="34"/>
+      <c r="H37" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="33">
